--- a/SDI_comparison_table_INDvsCTRL.xlsx
+++ b/SDI_comparison_table_INDvsCTRL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emeline/PROJECTS/connectome_epilepsy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABD3A36-6C6A-3C40-97D7-FD7D66A1CD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9F5132-B03F-E44A-9E84-0AA8814B145F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,18 +25,6 @@
     <t>ROI</t>
   </si>
   <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>HC</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
     <t>medialorbitofrontal_1</t>
   </si>
   <si>
@@ -86,6 +74,18 @@
   </si>
   <si>
     <t>Left-Hippocampus</t>
+  </si>
+  <si>
+    <t>EEG LT</t>
+  </si>
+  <si>
+    <t>EEG RT</t>
+  </si>
+  <si>
+    <t>SC HC</t>
+  </si>
+  <si>
+    <t>SC IND</t>
   </si>
 </sst>
 </file>
@@ -147,10 +147,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,276 +463,276 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2"/>
+      <c r="B1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2">
+        <v>-0.61</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2">
+        <v>-0.91</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2">
+        <v>-2.34</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2">
+        <v>-2.4</v>
+      </c>
+      <c r="D12" s="2">
+        <v>-0.93</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2">
+        <v>-1.59</v>
+      </c>
+      <c r="D13" s="2">
+        <v>-0.64</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>-2.12</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>-1.28</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2">
+        <v>-1.39</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2">
+        <v>-1.32</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="B19" s="2">
+        <v>-1.59</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2">
+        <v>-0.88</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2">
+        <v>-2.17</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3">
-        <v>-0.61</v>
-      </c>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3">
-        <v>-0.91</v>
-      </c>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3">
-        <v>-0.03</v>
-      </c>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2">
+        <v>-1.94</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="2">
+        <v>-2.11</v>
+      </c>
+      <c r="C22" s="2">
         <v>-2.34</v>
       </c>
-      <c r="E11" s="3">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3">
-        <v>-2.4</v>
-      </c>
-      <c r="D12" s="3">
-        <v>-0.93</v>
-      </c>
-      <c r="E12" s="3">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3">
-        <v>-1.59</v>
-      </c>
-      <c r="D13" s="3">
-        <v>-0.64</v>
-      </c>
-      <c r="E13" s="3">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="3">
-        <v>-2.12</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="3">
-        <v>-1.28</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3">
-        <v>-1.39</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3">
-        <v>-1.32</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="3">
-        <v>-1.59</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3">
-        <v>-0.88</v>
-      </c>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3">
-        <v>-2.17</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3">
-        <v>-1.94</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3">
-        <v>-2.11</v>
-      </c>
-      <c r="C22" s="3">
-        <v>-2.34</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2">
         <v>-1.81</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="2">
         <v>-0.2</v>
       </c>
-      <c r="E23" s="3"/>
+      <c r="E23" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
